--- a/implementation/security-readiness/portfolio/portfolio.xlsx
+++ b/implementation/security-readiness/portfolio/portfolio.xlsx
@@ -6293,7 +6293,7 @@
 **How to verify:**
 1. Sample production logs and telemetry for content and credentials.
 **Suggested fix:** Audit logs/telemetry payloads and enforce redaction/minimization.
-**Evidence so far:** implementation/AI_ENGINEERING_HARDENING_PLAN.md
+**Evidence so far:** implementation/ENGINEERING_PLAN.md
 **Evidence required to close:** Logging policy and sampled traces.
 **Standards:** OWASP Logging Cheat Sheet, OWASP LLM02:2025</t>
         </is>
@@ -7093,7 +7093,7 @@
 **How to verify:**
 1. Find yesterday's cost by operation and the top-spending user.
 **Suggested fix:** Add privacy-conscious AI tracing and operation/user/global budgets.
-**Evidence so far:** evals/rag/README.md, implementation/AI_ENGINEERING_HARDENING_PLAN.md
+**Evidence so far:** evals/rag/README.md, implementation/ENGINEERING_PLAN.md
 **Evidence required to close:** Telemetry schema/dashboard/query evidence.
 **Standards:** OWASP LLM10:2025, NIST AI RMF MANAGE 4</t>
         </is>
@@ -7622,7 +7622,7 @@
 **How to verify:**
 1. Pick a stored answer and identify the exact model and prompt that produced it.
 **Suggested fix:** Adopt one AI trace/version envelope across all provider calls.
-**Evidence so far:** packages/ai/src/coach.ts, implementation/AI_ENGINEERING_HARDENING_PLAN.md
+**Evidence so far:** packages/ai/src/coach.ts, implementation/ENGINEERING_PLAN.md
 **Evidence required to close:** Versioned configs/traces and reproducibility test.
 **Standards:** NIST AI RMF MEASURE 2, NIST AI 600-1: Information Integrity</t>
         </is>
@@ -7711,7 +7711,7 @@
 1. Compare the inventory with deployed services, environment variables and provider dashboards.
 2. Trace one sensitive record from intake to deletion and confirm every hop is documented.
 **Suggested fix:** Create security threat model/data-flow map and keep it synchronized with production components.
-**Evidence so far:** docs/ARCHITECTURE.md, implementation/AI_SOFTWARE_ENGINEERING_WALKTHROUGH.md
+**Evidence so far:** docs/ARCHITECTURE.md, ENGINEERING.md
 **Evidence required to close:** Current data-flow/trust-boundary diagram and component inventory.
 **Standards:** NIST SSDF PO.1, NIST AI RMF MAP 1, OWASP Top 10:2021 A04</t>
         </is>
@@ -14938,7 +14938,7 @@
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t xml:space="preserve">docs/ARCHITECTURE.md|implementation/AI_SOFTWARE_ENGINEERING_WALKTHROUGH.md</t>
+          <t xml:space="preserve">docs/ARCHITECTURE.md|ENGINEERING.md</t>
         </is>
       </c>
       <c r="W51" t="inlineStr">
@@ -19165,7 +19165,7 @@
       </c>
       <c r="U81" t="inlineStr">
         <is>
-          <t xml:space="preserve">packages/ai/src/coach.ts|implementation/AI_ENGINEERING_HARDENING_PLAN.md</t>
+          <t xml:space="preserve">packages/ai/src/coach.ts|implementation/ENGINEERING_PLAN.md</t>
         </is>
       </c>
       <c r="W81" t="inlineStr">
@@ -19304,7 +19304,7 @@
       </c>
       <c r="U82" t="inlineStr">
         <is>
-          <t xml:space="preserve">evals/rag/README.md|implementation/AI_ENGINEERING_HARDENING_PLAN.md</t>
+          <t xml:space="preserve">evals/rag/README.md|implementation/ENGINEERING_PLAN.md</t>
         </is>
       </c>
       <c r="W82" t="inlineStr">
@@ -20737,7 +20737,7 @@
       </c>
       <c r="U92" t="inlineStr">
         <is>
-          <t xml:space="preserve">implementation/AI_ENGINEERING_HARDENING_PLAN.md</t>
+          <t xml:space="preserve">implementation/ENGINEERING_PLAN.md</t>
         </is>
       </c>
       <c r="W92" t="inlineStr">
@@ -23601,7 +23601,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">implementation/AI_SOFTWARE_ENGINEERING_WALKTHROUGH.md</t>
+          <t xml:space="preserve">ENGINEERING.md</t>
         </is>
       </c>
     </row>
@@ -25545,7 +25545,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t xml:space="preserve">implementation/AI_ENGINEERING_HARDENING_PLAN.md</t>
+          <t xml:space="preserve">implementation/ENGINEERING_PLAN.md</t>
         </is>
       </c>
     </row>
@@ -25599,7 +25599,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t xml:space="preserve">implementation/AI_ENGINEERING_HARDENING_PLAN.md</t>
+          <t xml:space="preserve">implementation/ENGINEERING_PLAN.md</t>
         </is>
       </c>
     </row>
@@ -26166,7 +26166,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t xml:space="preserve">implementation/AI_ENGINEERING_HARDENING_PLAN.md</t>
+          <t xml:space="preserve">implementation/ENGINEERING_PLAN.md</t>
         </is>
       </c>
     </row>
